--- a/gestion_cobranza/20251229_req17333_Mantenedor_deudores/doc/deudores.xlsx
+++ b/gestion_cobranza/20251229_req17333_Mantenedor_deudores/doc/deudores.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\J\RepositorioJ_github\repositorioJ\gestion_cobranza\20251229_req17333_Mantenedor_deudores\doc\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9075"/>
   </bookViews>
   <sheets>
     <sheet name="deudores" sheetId="1" r:id="rId1"/>
@@ -19,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
   <si>
     <t>DDR_RUT</t>
   </si>
@@ -193,12 +188,21 @@
   </si>
   <si>
     <t>XXX</t>
+  </si>
+  <si>
+    <t>JJ</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>E</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -499,7 +503,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -507,8 +511,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="250" bestFit="1" customWidth="1"/>
@@ -520,12 +524,13 @@
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="250" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" customWidth="1"/>
     <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -581,7 +586,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -613,7 +618,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -633,7 +638,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -653,7 +658,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -673,7 +678,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -693,7 +698,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -713,7 +718,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -733,7 +738,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -753,7 +758,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -770,7 +775,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -788,6 +793,20 @@
       </c>
       <c r="G11">
         <v>33449421666</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="N12" t="s">
+        <v>59</v>
+      </c>
+      <c r="P12" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/gestion_cobranza/20251229_req17333_Mantenedor_deudores/doc/deudores.xlsx
+++ b/gestion_cobranza/20251229_req17333_Mantenedor_deudores/doc/deudores.xlsx
@@ -181,9 +181,6 @@
     <t>VALLES DE HUIN GANAL PARCELA 193</t>
   </si>
   <si>
-    <t>SANDRA MILENA HURTADO LAISECAXXX</t>
-  </si>
-  <si>
     <t>AV. MATTA 840XXX</t>
   </si>
   <si>
@@ -197,6 +194,9 @@
   </si>
   <si>
     <t>E</t>
+  </si>
+  <si>
+    <t>SANDRA MILENA HURTADO LAISECA</t>
   </si>
 </sst>
 </file>
@@ -503,7 +503,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -591,13 +591,13 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
         <v>55</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>56</v>
-      </c>
-      <c r="D2" t="s">
-        <v>57</v>
       </c>
       <c r="E2">
         <v>1300</v>
@@ -800,13 +800,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" t="s">
         <v>58</v>
       </c>
-      <c r="N12" t="s">
+      <c r="P12" t="s">
         <v>59</v>
-      </c>
-      <c r="P12" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
